--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487031_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487031_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6005</v>
+        <v>5.7494</v>
       </c>
       <c r="E2" t="n">
-        <v>5.005</v>
+        <v>3.6625</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5955</v>
+        <v>2.0869</v>
       </c>
       <c r="G2" t="n">
         <v>1.4614</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1741</v>
+        <v>2.323</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0829</v>
+        <v>1.7404</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0912</v>
+        <v>0.5826</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4521</v>
+        <v>4.8562</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8435</v>
+        <v>1.7027</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6086</v>
+        <v>3.1535</v>
       </c>
       <c r="G3" t="n">
         <v>0.86</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4799</v>
+        <v>0.8841</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0061</v>
+        <v>0.8653</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4739</v>
+        <v>0.0188</v>
       </c>
       <c r="V3" t="n">
         <v>3.1122</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3146</v>
+        <v>4.2228</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0062</v>
+        <v>1.5664</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3084</v>
+        <v>2.6564</v>
       </c>
       <c r="G4" t="n">
         <v>4.4464</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6299</v>
+        <v>0.2783</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2551</v>
+        <v>0.3051</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3748</v>
+        <v>-0.0268</v>
       </c>
       <c r="V4" t="n">
         <v>0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4375</v>
+        <v>2.1375</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6183</v>
+        <v>0.2424</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0558</v>
+        <v>1.8952</v>
       </c>
       <c r="G5" t="n">
         <v>-0.525</v>
@@ -844,13 +844,13 @@
         <v>2.7021</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9373</v>
+        <v>-0.2373</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9373</v>
+        <v>-0.0766</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>-0.1607</v>
       </c>
       <c r="V5" t="n">
         <v>2.1278</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0629</v>
+        <v>0.6776</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8356</v>
+        <v>-0.435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8985</v>
+        <v>1.1127</v>
       </c>
       <c r="G6" t="n">
         <v>0.3407</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3127</v>
+        <v>-0.698</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5208</v>
+        <v>-0.1203</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7919</v>
+        <v>-0.5777</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5891</v>
+        <v>0.2725</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3977</v>
+        <v>0.3033</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1914</v>
+        <v>-0.0308</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0414</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6359</v>
+        <v>0.2257</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2551</v>
+        <v>0.4459</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3808</v>
+        <v>-0.2201</v>
       </c>
       <c r="V7" t="n">
         <v>-1.842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.9313</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3234</v>
+        <v>-0.6238</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3878</v>
+        <v>-0.3075</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3874</v>
@@ -1078,13 +1078,13 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2902</v>
+        <v>0.0701</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3702</v>
+        <v>0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2086</v>
+        <v>-1.6008</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8273</v>
+        <v>-3.3266</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6187</v>
+        <v>1.7258</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4269</v>
@@ -1156,13 +1156,13 @@
         <v>2.7021</v>
       </c>
       <c r="S9" t="n">
-        <v>0.427</v>
+        <v>1.0348</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4125</v>
+        <v>0.9132</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0145</v>
+        <v>0.1216</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8576</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4174</v>
+        <v>-3.5102</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2865</v>
+        <v>-3.2718</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1309</v>
+        <v>-0.2384</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2635</v>
+        <v>-2.9353</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1551</v>
+        <v>-0.9667</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1085</v>
+        <v>-1.9685</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5509</v>
+        <v>-3.2559</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5888</v>
+        <v>-1.2938</v>
       </c>
       <c r="L10" t="n">
         <v>-1.9621</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2874</v>
+        <v>0.3207</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4338</v>
+        <v>0.3271</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1464</v>
+        <v>-0.0064</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="R10" t="n">
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4601</v>
+        <v>0.074</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4225</v>
+        <v>0.1772</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0377</v>
+        <v>-0.1031</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9702</v>
+        <v>-4.0986</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7318</v>
+        <v>-3.8873</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2384</v>
+        <v>-0.2112</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9353</v>
+        <v>-3.2635</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9667</v>
+        <v>-1.1551</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9685</v>
+        <v>-2.1085</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.2559</v>
+        <v>-3.5509</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2938</v>
+        <v>-1.5888</v>
       </c>
       <c r="L11" t="n">
         <v>-1.9621</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3207</v>
+        <v>0.2874</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3271</v>
+        <v>0.4338</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0064</v>
+        <v>-0.1464</v>
       </c>
       <c r="P11" t="n">
-        <v>0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="R11" t="n">
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.386</v>
+        <v>0.779</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2829</v>
+        <v>0.8216</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1031</v>
+        <v>-0.0427</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9545</v>
+        <v>-5.4611</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1987</v>
+        <v>-5.9999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2443</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5051</v>
@@ -1390,13 +1390,13 @@
         <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7087</v>
+        <v>1.202</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8667</v>
+        <v>1.0656</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.158</v>
+        <v>0.1365</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.016599999999998</v>
+        <v>2.313999999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.3646</v>
+        <v>-10.0671</v>
       </c>
       <c r="F13" t="n">
-        <v>12.3813</v>
+        <v>12.3814</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9761</v>
@@ -1459,7 +1459,7 @@
         <v>3.8448</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.3358</v>
@@ -1468,13 +1468,13 @@
         <v>18.3358</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6382</v>
+        <v>5.9357</v>
       </c>
       <c r="T13" t="n">
-        <v>5.909700000000001</v>
+        <v>6.2071</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2713</v>
+        <v>-0.2712999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.354600000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7382</v>
+        <v>2.5342</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.09429999999999999</v>
+        <v>1.0959</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8325</v>
+        <v>1.4383</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2134</v>
+        <v>1.6245</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5697</v>
+        <v>0.265</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3563</v>
+        <v>1.3595</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5727</v>
+        <v>0.7225</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1511</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5783</v>
+        <v>1.2453</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3594</v>
+        <v>0.9019</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5814</v>
+        <v>0.7877</v>
       </c>
       <c r="O14" t="n">
-        <v>0.222</v>
+        <v>0.1142</v>
       </c>
       <c r="P14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-3.8602</v>
-      </c>
       <c r="R14" t="n">
-        <v>2.8951</v>
+        <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9604</v>
+        <v>-0.3183</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6637</v>
+        <v>0.1104</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2967</v>
+        <v>-0.4287</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5295</v>
+        <v>1.228</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5295</v>
+        <v>1.228</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7077</v>
+        <v>2.5074</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2962</v>
+        <v>-0.7139</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4115</v>
+        <v>3.2213</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6245</v>
+        <v>4.645</v>
       </c>
       <c r="H15" t="n">
-        <v>0.265</v>
+        <v>3.0885</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3595</v>
+        <v>1.5566</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7225</v>
+        <v>2.3216</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5227000000000001</v>
+        <v>2.3545</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2453</v>
+        <v>-0.0328</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9019</v>
+        <v>2.3234</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7877</v>
+        <v>0.734</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1142</v>
+        <v>1.5894</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>-0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1448</v>
+        <v>-1.1799</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3107</v>
+        <v>-0.4263</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4554</v>
+        <v>-0.7536</v>
       </c>
       <c r="V15" t="n">
-        <v>1.228</v>
+        <v>-0.5717</v>
       </c>
       <c r="W15" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6924</v>
+        <v>2.1162</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9142</v>
+        <v>-0.3947</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6066</v>
+        <v>2.5109</v>
       </c>
       <c r="G16" t="n">
-        <v>4.645</v>
+        <v>2.2134</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0885</v>
+        <v>2.5697</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5566</v>
+        <v>-0.3563</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3216</v>
+        <v>2.5727</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3545</v>
+        <v>3.1511</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0328</v>
+        <v>-0.5783</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3234</v>
+        <v>-0.3594</v>
       </c>
       <c r="N16" t="n">
-        <v>0.734</v>
+        <v>-0.5814</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5894</v>
+        <v>0.222</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>2.8951</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9949</v>
+        <v>0.3384</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6266</v>
+        <v>0.3633</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3683</v>
+        <v>-0.0248</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5717</v>
+        <v>0.5295</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2859</v>
+        <v>0.5295</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0432</v>
+        <v>1.0967</v>
       </c>
       <c r="E17" t="n">
         <v>0.5118</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5314</v>
+        <v>0.5849</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0711</v>
@@ -1780,13 +1780,13 @@
         <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2723</v>
+        <v>0.3259</v>
       </c>
       <c r="T17" t="n">
         <v>0.1468</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1256</v>
+        <v>0.1791</v>
       </c>
       <c r="V17" t="n">
         <v>1.228</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8418</v>
+        <v>0.6805</v>
       </c>
       <c r="E18" t="n">
         <v>2.2501</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4083</v>
+        <v>-1.5695</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1798</v>
@@ -1858,13 +1858,13 @@
         <v>1.7371</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3874</v>
+        <v>-0.5486</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0766</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3107</v>
+        <v>-0.472</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3281</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3675</v>
+        <v>0.5212</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6093</v>
+        <v>-0.5092</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9769</v>
+        <v>1.0304</v>
       </c>
       <c r="G19" t="n">
         <v>0.5948</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3503</v>
+        <v>-0.1966</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4164</v>
+        <v>-0.3163</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3087</v>
+        <v>-0.3549</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3118</v>
+        <v>-1.8125</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0031</v>
+        <v>1.4576</v>
       </c>
       <c r="G21" t="n">
         <v>1.0453</v>
@@ -2092,13 +2092,13 @@
         <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6471</v>
+        <v>-0.6934</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7086</v>
+        <v>0.2079</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3557</v>
+        <v>-0.9013</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8999</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3973</v>
+        <v>-1.0299</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.123</v>
+        <v>-3.2281</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7257</v>
+        <v>2.1983</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8028</v>
+        <v>0.5264</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5471</v>
+        <v>0.0073</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2556</v>
+        <v>0.5191</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5426</v>
+        <v>0.2182</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8993</v>
+        <v>0.4552</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6433</v>
+        <v>-0.237</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2601</v>
+        <v>0.3082</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6478</v>
+        <v>-0.4479</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3877</v>
+        <v>0.7561</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3511</v>
+        <v>-0.965</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3511</v>
+        <v>2.8951</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2737</v>
+        <v>-1.1207</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5803</v>
+        <v>-0.1156</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6934</v>
+        <v>-1.0051</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3281</v>
+        <v>0.5295</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5295</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6725</v>
+        <v>-1.8365</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.393</v>
+        <v>-2.7224</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2794</v>
+        <v>0.886</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3504</v>
+        <v>-2.8028</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8259</v>
+        <v>-2.5471</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4755</v>
+        <v>-0.2556</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1917</v>
+        <v>-2.5426</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2731</v>
+        <v>-1.8993</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0814</v>
+        <v>-0.6433</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8413</v>
+        <v>-0.2601</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4472</v>
+        <v>-0.6478</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3941</v>
+        <v>0.3877</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>1.392</v>
+        <v>-0.7129</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4079</v>
+        <v>-0.1798</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0159</v>
+        <v>-0.5331</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1701</v>
+        <v>0.3281</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4559</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7959</v>
+        <v>-2.7288</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3248</v>
+        <v>-3.5251</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5289</v>
+        <v>0.7962</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0827</v>
@@ -2326,13 +2326,13 @@
         <v>0.386</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1342</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3107</v>
+        <v>0.1104</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1804</v>
+        <v>-3.4673</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6301</v>
+        <v>-3.2943</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4497</v>
+        <v>-0.173</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5264</v>
+        <v>-0.3504</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0073</v>
+        <v>-0.8259</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5191</v>
+        <v>0.4755</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2182</v>
+        <v>-1.1917</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4552</v>
+        <v>-1.2731</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.237</v>
+        <v>0.0814</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3082</v>
+        <v>0.8413</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4479</v>
+        <v>0.4472</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7561</v>
+        <v>0.3941</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.965</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R25" t="n">
-        <v>2.8951</v>
+        <v>1.3511</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.2712</v>
+        <v>0.5972</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5176</v>
+        <v>0.5067</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7536</v>
+        <v>0.0905</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5295</v>
+        <v>-2.1701</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5295</v>
+        <v>0.2859</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="26">
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0168</v>
+        <v>-0.0139999999999989</v>
       </c>
       <c r="E26" t="n">
         <v>-12.3812</v>
       </c>
       <c r="F26" t="n">
-        <v>10.3646</v>
+        <v>12.3674</v>
       </c>
       <c r="G26" t="n">
-        <v>4.976300000000001</v>
+        <v>4.976300000000002</v>
       </c>
       <c r="H26" t="n">
         <v>3.7054</v>
       </c>
       <c r="I26" t="n">
-        <v>1.271</v>
+        <v>1.271000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2030999999999996</v>
+        <v>-0.2030999999999992</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6419</v>
+        <v>3.641899999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-3.8447</v>
@@ -2467,13 +2467,13 @@
         <v>5.1793</v>
       </c>
       <c r="N26" t="n">
-        <v>0.06349999999999983</v>
+        <v>0.06349999999999989</v>
       </c>
       <c r="O26" t="n">
-        <v>5.1157</v>
+        <v>5.115699999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.000200000000000311</v>
+        <v>0.000199999999999978</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.3357</v>
@@ -2482,13 +2482,13 @@
         <v>18.3358</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.6384</v>
+        <v>-3.6355</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2713999999999999</v>
+        <v>0.2714</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.9095</v>
+        <v>-3.9069</v>
       </c>
       <c r="V26" t="n">
         <v>-1.3547</v>
